--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:32:05+00:00</t>
+    <t>2026-04-22T13:26:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T13:26:00+00:00</t>
+    <t>2026-05-04T08:14:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:14:07+00:00</t>
+    <t>2026-05-13T07:14:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T07:14:42+00:00</t>
+    <t>2026-06-10T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T08:49:37+00:00</t>
+    <t>2026-06-10T08:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T08:50:04+00:00</t>
+    <t>2026-06-10T08:52:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T08:52:37+00:00</t>
+    <t>2026-06-16T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -105,13 +105,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/BL</t>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/BL|2.0.0-sd</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/boolean</t>
+    <t>http://hl7.org/fhir/StructureDefinition/boolean|4.0.1</t>
   </si>
   <si>
     <t>BL.value</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:17:05+00:00</t>
+    <t>2026-06-17T07:57:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:57:57+00:00</t>
+    <t>2026-06-17T09:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:34:17+00:00</t>
+    <t>2026-06-18T08:47:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:47:35+00:00</t>
+    <t>2026-06-18T09:44:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:44:31+00:00</t>
+    <t>2026-06-18T10:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:42:22+00:00</t>
+    <t>2026-06-18T10:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:44:43+00:00</t>
+    <t>2026-06-26T12:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:07:29+00:00</t>
+    <t>2026-06-30T14:53:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:53:19+00:00</t>
+    <t>2026-07-02T14:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T14:54:00+00:00</t>
+    <t>2026-07-02T14:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T14:58:37+00:00</t>
+    <t>2026-07-07T15:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T15:31:37+00:00</t>
+    <t>2026-07-07T15:40:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T15:40:33+00:00</t>
+    <t>2026-07-15T11:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T11:54:19+00:00</t>
+    <t>2026-07-17T07:40:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T07:40:05+00:00</t>
+    <t>2026-07-17T13:13:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T13:13:19+00:00</t>
+    <t>2026-07-20T12:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T12:36:25+00:00</t>
+    <t>2026-07-31T12:50:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:50:31+00:00</t>
+    <t>2026-07-31T12:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/main/ig/CdaBLToBooleanConceptMap.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/mappingcdafhir/ConceptMap/DataTypes/CdaBLToFHIR</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/mappingcdafhir/ConceptMap/CdaBLToBooleanConceptMap</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:55:21+00:00</t>
+    <t>2026-07-31T13:43:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>boolean</t>
+  </si>
+  <si>
+    <t>Primitive Type boolean</t>
   </si>
 </sst>
 </file>
@@ -427,7 +430,7 @@
         <v>35</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
